--- a/local/templates/competitionResults/BARS-Results.xlsx
+++ b/local/templates/competitionResults/BARS-Results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/scottgonzalez/Projects/nemikor/usaw-owlcms/local/templates/competitionResults/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18AB9C17-5EFF-964D-902F-4A6931D1621C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ED11338-B323-4548-A90A-2B2FC57543DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1540" yWindow="660" windowWidth="33020" windowHeight="21680" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1540" yWindow="660" windowWidth="33020" windowHeight="21680" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" r:id="rId1"/>
@@ -108,7 +108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="306">
   <si>
     <t>Lifter Membership ID</t>
   </si>
@@ -374,12 +374,6 @@
     <t>Open W</t>
   </si>
   <si>
-    <t>ADAP M</t>
-  </si>
-  <si>
-    <t>ADAP W</t>
-  </si>
-  <si>
     <t>MIL M</t>
   </si>
   <si>
@@ -398,126 +392,6 @@
     <t>Women's</t>
   </si>
   <si>
-    <t>ADAP U25 M</t>
-  </si>
-  <si>
-    <t>ADAP U25 W</t>
-  </si>
-  <si>
-    <t>ADAP U17 M</t>
-  </si>
-  <si>
-    <t>ADAP U17 W</t>
-  </si>
-  <si>
-    <t>ADAP U15 M</t>
-  </si>
-  <si>
-    <t>ADAP U15 W</t>
-  </si>
-  <si>
-    <t>ADAP U13 M</t>
-  </si>
-  <si>
-    <t>ADAP U13 W</t>
-  </si>
-  <si>
-    <t>ADAP U11 M</t>
-  </si>
-  <si>
-    <t>ADAP U11 W</t>
-  </si>
-  <si>
-    <t>ADAP JR M</t>
-  </si>
-  <si>
-    <t>ADAP JR W</t>
-  </si>
-  <si>
-    <t>ADAP M35</t>
-  </si>
-  <si>
-    <t>ADAP W35</t>
-  </si>
-  <si>
-    <t>ADAP M40</t>
-  </si>
-  <si>
-    <t>ADAP W40</t>
-  </si>
-  <si>
-    <t>ADAP M45</t>
-  </si>
-  <si>
-    <t>ADAP W45</t>
-  </si>
-  <si>
-    <t>ADAP M50</t>
-  </si>
-  <si>
-    <t>ADAP W50</t>
-  </si>
-  <si>
-    <t>ADAP M55</t>
-  </si>
-  <si>
-    <t>ADAP W55</t>
-  </si>
-  <si>
-    <t>ADAP M60</t>
-  </si>
-  <si>
-    <t>ADAP W60</t>
-  </si>
-  <si>
-    <t>ADAP M65</t>
-  </si>
-  <si>
-    <t>ADAP W65</t>
-  </si>
-  <si>
-    <t>ADAP M70</t>
-  </si>
-  <si>
-    <t>ADAP W70</t>
-  </si>
-  <si>
-    <t>ADAP M75</t>
-  </si>
-  <si>
-    <t>ADAP W75</t>
-  </si>
-  <si>
-    <t>ADAP M80</t>
-  </si>
-  <si>
-    <t>ADAP W80</t>
-  </si>
-  <si>
-    <t>ADAP M85</t>
-  </si>
-  <si>
-    <t>ADAP W85</t>
-  </si>
-  <si>
-    <t>ADAP M90</t>
-  </si>
-  <si>
-    <t>ADAP W90</t>
-  </si>
-  <si>
-    <t>ADAP M95</t>
-  </si>
-  <si>
-    <t>ADAP W95</t>
-  </si>
-  <si>
-    <t>ADAP M100</t>
-  </si>
-  <si>
-    <t>ADAP W100</t>
-  </si>
-  <si>
     <t>WSO U25 M</t>
   </si>
   <si>
@@ -648,6 +522,510 @@
   </si>
   <si>
     <t>Women's 11 Under Age Group</t>
+  </si>
+  <si>
+    <t>ADP U25 M</t>
+  </si>
+  <si>
+    <t>ADP U25 W</t>
+  </si>
+  <si>
+    <t>ADP U17 M</t>
+  </si>
+  <si>
+    <t>ADP U17 W</t>
+  </si>
+  <si>
+    <t>ADP U15 M</t>
+  </si>
+  <si>
+    <t>ADP U15 W</t>
+  </si>
+  <si>
+    <t>ADP U13 M</t>
+  </si>
+  <si>
+    <t>ADP U13 W</t>
+  </si>
+  <si>
+    <t>ADP U11 M</t>
+  </si>
+  <si>
+    <t>ADP U11 W</t>
+  </si>
+  <si>
+    <t>ADP JR M</t>
+  </si>
+  <si>
+    <t>ADP JR W</t>
+  </si>
+  <si>
+    <t>ADP M</t>
+  </si>
+  <si>
+    <t>ADP W</t>
+  </si>
+  <si>
+    <t>ADP M35</t>
+  </si>
+  <si>
+    <t>ADP W35</t>
+  </si>
+  <si>
+    <t>ADP M40</t>
+  </si>
+  <si>
+    <t>ADP W40</t>
+  </si>
+  <si>
+    <t>ADP M45</t>
+  </si>
+  <si>
+    <t>ADP W45</t>
+  </si>
+  <si>
+    <t>ADP M50</t>
+  </si>
+  <si>
+    <t>ADP W50</t>
+  </si>
+  <si>
+    <t>ADP M55</t>
+  </si>
+  <si>
+    <t>ADP W55</t>
+  </si>
+  <si>
+    <t>ADP M60</t>
+  </si>
+  <si>
+    <t>ADP W60</t>
+  </si>
+  <si>
+    <t>ADP M65</t>
+  </si>
+  <si>
+    <t>ADP W65</t>
+  </si>
+  <si>
+    <t>ADP M70</t>
+  </si>
+  <si>
+    <t>ADP W70</t>
+  </si>
+  <si>
+    <t>ADP M75</t>
+  </si>
+  <si>
+    <t>ADP W75</t>
+  </si>
+  <si>
+    <t>ADP M80</t>
+  </si>
+  <si>
+    <t>ADP W80</t>
+  </si>
+  <si>
+    <t>ADP M85</t>
+  </si>
+  <si>
+    <t>ADP W85</t>
+  </si>
+  <si>
+    <t>ADP M90</t>
+  </si>
+  <si>
+    <t>ADP W90</t>
+  </si>
+  <si>
+    <t>ADP M95</t>
+  </si>
+  <si>
+    <t>ADP W95</t>
+  </si>
+  <si>
+    <t>ADP M100</t>
+  </si>
+  <si>
+    <t>ADP W100</t>
+  </si>
+  <si>
+    <t>ADH U25 M</t>
+  </si>
+  <si>
+    <t>ADH U25 W</t>
+  </si>
+  <si>
+    <t>ADH U17 M</t>
+  </si>
+  <si>
+    <t>ADH U17 W</t>
+  </si>
+  <si>
+    <t>ADH U15 M</t>
+  </si>
+  <si>
+    <t>ADH U15 W</t>
+  </si>
+  <si>
+    <t>ADH U13 M</t>
+  </si>
+  <si>
+    <t>ADH U13 W</t>
+  </si>
+  <si>
+    <t>ADH U11 M</t>
+  </si>
+  <si>
+    <t>ADH U11 W</t>
+  </si>
+  <si>
+    <t>ADH JR M</t>
+  </si>
+  <si>
+    <t>ADH JR W</t>
+  </si>
+  <si>
+    <t>ADH M</t>
+  </si>
+  <si>
+    <t>ADH W</t>
+  </si>
+  <si>
+    <t>ADH M35</t>
+  </si>
+  <si>
+    <t>ADH W35</t>
+  </si>
+  <si>
+    <t>ADH M40</t>
+  </si>
+  <si>
+    <t>ADH W40</t>
+  </si>
+  <si>
+    <t>ADH M45</t>
+  </si>
+  <si>
+    <t>ADH W45</t>
+  </si>
+  <si>
+    <t>ADH M50</t>
+  </si>
+  <si>
+    <t>ADH W50</t>
+  </si>
+  <si>
+    <t>ADH M55</t>
+  </si>
+  <si>
+    <t>ADH W55</t>
+  </si>
+  <si>
+    <t>ADH M60</t>
+  </si>
+  <si>
+    <t>ADH W60</t>
+  </si>
+  <si>
+    <t>ADH M65</t>
+  </si>
+  <si>
+    <t>ADH W65</t>
+  </si>
+  <si>
+    <t>ADH M70</t>
+  </si>
+  <si>
+    <t>ADH W70</t>
+  </si>
+  <si>
+    <t>ADH M75</t>
+  </si>
+  <si>
+    <t>ADH W75</t>
+  </si>
+  <si>
+    <t>ADH M80</t>
+  </si>
+  <si>
+    <t>ADH W80</t>
+  </si>
+  <si>
+    <t>ADH M85</t>
+  </si>
+  <si>
+    <t>ADH W85</t>
+  </si>
+  <si>
+    <t>ADH M90</t>
+  </si>
+  <si>
+    <t>ADH W90</t>
+  </si>
+  <si>
+    <t>ADH M95</t>
+  </si>
+  <si>
+    <t>ADH W95</t>
+  </si>
+  <si>
+    <t>ADH M100</t>
+  </si>
+  <si>
+    <t>ADH W100</t>
+  </si>
+  <si>
+    <t>ADI U25 M</t>
+  </si>
+  <si>
+    <t>ADI U25 W</t>
+  </si>
+  <si>
+    <t>ADI U17 M</t>
+  </si>
+  <si>
+    <t>ADI U17 W</t>
+  </si>
+  <si>
+    <t>ADI U15 M</t>
+  </si>
+  <si>
+    <t>ADI U15 W</t>
+  </si>
+  <si>
+    <t>ADI U13 M</t>
+  </si>
+  <si>
+    <t>ADI U13 W</t>
+  </si>
+  <si>
+    <t>ADI U11 M</t>
+  </si>
+  <si>
+    <t>ADI U11 W</t>
+  </si>
+  <si>
+    <t>ADI JR M</t>
+  </si>
+  <si>
+    <t>ADI JR W</t>
+  </si>
+  <si>
+    <t>ADI M</t>
+  </si>
+  <si>
+    <t>ADI W</t>
+  </si>
+  <si>
+    <t>ADI M35</t>
+  </si>
+  <si>
+    <t>ADI W35</t>
+  </si>
+  <si>
+    <t>ADI M40</t>
+  </si>
+  <si>
+    <t>ADI W40</t>
+  </si>
+  <si>
+    <t>ADI M45</t>
+  </si>
+  <si>
+    <t>ADI W45</t>
+  </si>
+  <si>
+    <t>ADI M50</t>
+  </si>
+  <si>
+    <t>ADI W50</t>
+  </si>
+  <si>
+    <t>ADI M55</t>
+  </si>
+  <si>
+    <t>ADI W55</t>
+  </si>
+  <si>
+    <t>ADI M60</t>
+  </si>
+  <si>
+    <t>ADI W60</t>
+  </si>
+  <si>
+    <t>ADI M65</t>
+  </si>
+  <si>
+    <t>ADI W65</t>
+  </si>
+  <si>
+    <t>ADI M70</t>
+  </si>
+  <si>
+    <t>ADI W70</t>
+  </si>
+  <si>
+    <t>ADI M75</t>
+  </si>
+  <si>
+    <t>ADI W75</t>
+  </si>
+  <si>
+    <t>ADI M80</t>
+  </si>
+  <si>
+    <t>ADI W80</t>
+  </si>
+  <si>
+    <t>ADI M85</t>
+  </si>
+  <si>
+    <t>ADI W85</t>
+  </si>
+  <si>
+    <t>ADI M90</t>
+  </si>
+  <si>
+    <t>ADI W90</t>
+  </si>
+  <si>
+    <t>ADI M95</t>
+  </si>
+  <si>
+    <t>ADI W95</t>
+  </si>
+  <si>
+    <t>ADI M100</t>
+  </si>
+  <si>
+    <t>ADI W100</t>
+  </si>
+  <si>
+    <t>ADV U25 M</t>
+  </si>
+  <si>
+    <t>ADV U25 W</t>
+  </si>
+  <si>
+    <t>ADV U17 M</t>
+  </si>
+  <si>
+    <t>ADV U17 W</t>
+  </si>
+  <si>
+    <t>ADV U15 M</t>
+  </si>
+  <si>
+    <t>ADV U15 W</t>
+  </si>
+  <si>
+    <t>ADV U13 M</t>
+  </si>
+  <si>
+    <t>ADV U13 W</t>
+  </si>
+  <si>
+    <t>ADV U11 M</t>
+  </si>
+  <si>
+    <t>ADV U11 W</t>
+  </si>
+  <si>
+    <t>ADV JR M</t>
+  </si>
+  <si>
+    <t>ADV JR W</t>
+  </si>
+  <si>
+    <t>ADV M</t>
+  </si>
+  <si>
+    <t>ADV W</t>
+  </si>
+  <si>
+    <t>ADV M35</t>
+  </si>
+  <si>
+    <t>ADV W35</t>
+  </si>
+  <si>
+    <t>ADV M40</t>
+  </si>
+  <si>
+    <t>ADV W40</t>
+  </si>
+  <si>
+    <t>ADV M45</t>
+  </si>
+  <si>
+    <t>ADV W45</t>
+  </si>
+  <si>
+    <t>ADV M50</t>
+  </si>
+  <si>
+    <t>ADV W50</t>
+  </si>
+  <si>
+    <t>ADV M55</t>
+  </si>
+  <si>
+    <t>ADV W55</t>
+  </si>
+  <si>
+    <t>ADV M60</t>
+  </si>
+  <si>
+    <t>ADV W60</t>
+  </si>
+  <si>
+    <t>ADV M65</t>
+  </si>
+  <si>
+    <t>ADV W65</t>
+  </si>
+  <si>
+    <t>ADV M70</t>
+  </si>
+  <si>
+    <t>ADV W70</t>
+  </si>
+  <si>
+    <t>ADV M75</t>
+  </si>
+  <si>
+    <t>ADV W75</t>
+  </si>
+  <si>
+    <t>ADV M80</t>
+  </si>
+  <si>
+    <t>ADV W80</t>
+  </si>
+  <si>
+    <t>ADV M85</t>
+  </si>
+  <si>
+    <t>ADV W85</t>
+  </si>
+  <si>
+    <t>ADV M90</t>
+  </si>
+  <si>
+    <t>ADV W90</t>
+  </si>
+  <si>
+    <t>ADV M95</t>
+  </si>
+  <si>
+    <t>ADV W95</t>
+  </si>
+  <si>
+    <t>ADV M100</t>
+  </si>
+  <si>
+    <t>ADV W100</t>
   </si>
 </sst>
 </file>
@@ -756,11 +1134,11 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>2025650</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>101600</xdr:rowOff>
+      <xdr:colOff>3810</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>182880</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="4565992" cy="1418527"/>
+    <xdr:ext cx="6622324" cy="2294792"/>
     <xdr:sp macro="" textlink="" fLocksText="0">
       <xdr:nvSpPr>
         <xdr:cNvPr id="1025" name="TextBox 1">
@@ -776,8 +1154,8 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="4047490" y="802640"/>
-          <a:ext cx="4565992" cy="1418527"/>
+          <a:off x="2025650" y="680720"/>
+          <a:ext cx="6622324" cy="2294792"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -821,7 +1199,7 @@
             <a:defRPr sz="1000"/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-CA" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-CA" sz="1600" b="0" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
@@ -837,7 +1215,7 @@
             <a:defRPr sz="1000"/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-CA" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-CA" sz="1600" b="0" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
@@ -853,7 +1231,7 @@
             <a:defRPr sz="1000"/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-CA" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-CA" sz="1600" b="0" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
@@ -869,7 +1247,7 @@
             <a:defRPr sz="1000"/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-CA" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-CA" sz="1600" b="0" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
@@ -885,7 +1263,7 @@
             <a:defRPr sz="1000"/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-CA" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-CA" sz="1600" b="0" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
@@ -901,7 +1279,7 @@
             <a:defRPr sz="1000"/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-CA" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-CA" sz="1600" b="0" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
@@ -909,15 +1287,53 @@
               <a:ea typeface="Calibri"/>
               <a:cs typeface="Calibri"/>
             </a:rPr>
-            <a:t>    - keyboard shortcut (Ctrl-Alt-V followed by V) OR</a:t>
+            <a:t>    - keyboard shortcut on Windows (Ctrl-Alt-V followed by V) OR</a:t>
           </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr sz="1000"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-CA" sz="1600" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+            </a:rPr>
+            <a:t>    - keyboard shortcut on Mac (Cmd-Alt-V followed by V) OR</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-CA" sz="1600" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+          </a:endParaRPr>
         </a:p>
         <a:p>
           <a:pPr algn="l" rtl="0">
             <a:defRPr sz="1000"/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-CA" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-CA" sz="1600" b="0" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
@@ -933,7 +1349,7 @@
             <a:defRPr sz="1000"/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-CA" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-CA" sz="1600" b="0" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
@@ -1383,10 +1799,10 @@
         <v>72</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>73</v>
@@ -1443,7 +1859,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E128"/>
+  <dimension ref="A1:E254"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.5" bestFit="1" customWidth="1"/>
@@ -1457,7 +1873,7 @@
         <v>70</v>
       </c>
       <c r="B1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -1465,7 +1881,7 @@
         <v>81</v>
       </c>
       <c r="B2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -1521,7 +1937,7 @@
         <v>71</v>
       </c>
       <c r="B9" t="s">
-        <v>178</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -1529,7 +1945,7 @@
         <v>85</v>
       </c>
       <c r="B10" t="s">
-        <v>179</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -1553,7 +1969,7 @@
         <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
@@ -1561,23 +1977,23 @@
         <v>87</v>
       </c>
       <c r="B14" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B15" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B16" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
@@ -1808,23 +2224,23 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>96</v>
+        <v>180</v>
       </c>
       <c r="B45" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>97</v>
+        <v>181</v>
       </c>
       <c r="B46" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>98</v>
+        <v>182</v>
       </c>
       <c r="B47" t="s">
         <v>10</v>
@@ -1832,7 +2248,7 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>99</v>
+        <v>183</v>
       </c>
       <c r="B48" t="s">
         <v>12</v>
@@ -1840,7 +2256,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>100</v>
+        <v>184</v>
       </c>
       <c r="B49" t="s">
         <v>13</v>
@@ -1848,7 +2264,7 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>101</v>
+        <v>185</v>
       </c>
       <c r="B50" t="s">
         <v>15</v>
@@ -1856,7 +2272,7 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>102</v>
+        <v>186</v>
       </c>
       <c r="B51" t="s">
         <v>16</v>
@@ -1864,7 +2280,7 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>103</v>
+        <v>187</v>
       </c>
       <c r="B52" t="s">
         <v>18</v>
@@ -1872,23 +2288,23 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>104</v>
+        <v>188</v>
       </c>
       <c r="B53" t="s">
-        <v>178</v>
+        <v>136</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>105</v>
+        <v>189</v>
       </c>
       <c r="B54" t="s">
-        <v>179</v>
+        <v>137</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>106</v>
+        <v>190</v>
       </c>
       <c r="B55" t="s">
         <v>19</v>
@@ -1896,7 +2312,7 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>107</v>
+        <v>191</v>
       </c>
       <c r="B56" t="s">
         <v>21</v>
@@ -1904,23 +2320,23 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>88</v>
+        <v>192</v>
       </c>
       <c r="B57" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>89</v>
+        <v>193</v>
       </c>
       <c r="B58" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>108</v>
+        <v>194</v>
       </c>
       <c r="B59" t="s">
         <v>23</v>
@@ -1928,7 +2344,7 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>109</v>
+        <v>195</v>
       </c>
       <c r="B60" t="s">
         <v>25</v>
@@ -1936,7 +2352,7 @@
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="B61" t="s">
         <v>27</v>
@@ -1944,7 +2360,7 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>111</v>
+        <v>197</v>
       </c>
       <c r="B62" t="s">
         <v>29</v>
@@ -1952,7 +2368,7 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>112</v>
+        <v>198</v>
       </c>
       <c r="B63" t="s">
         <v>31</v>
@@ -1960,7 +2376,7 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="B64" t="s">
         <v>33</v>
@@ -1968,7 +2384,7 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="B65" t="s">
         <v>35</v>
@@ -1976,7 +2392,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>115</v>
+        <v>201</v>
       </c>
       <c r="B66" t="s">
         <v>37</v>
@@ -1984,7 +2400,7 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>116</v>
+        <v>202</v>
       </c>
       <c r="B67" t="s">
         <v>39</v>
@@ -1992,7 +2408,7 @@
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>117</v>
+        <v>203</v>
       </c>
       <c r="B68" t="s">
         <v>41</v>
@@ -2000,7 +2416,7 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>118</v>
+        <v>204</v>
       </c>
       <c r="B69" t="s">
         <v>43</v>
@@ -2008,7 +2424,7 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>119</v>
+        <v>205</v>
       </c>
       <c r="B70" t="s">
         <v>45</v>
@@ -2016,7 +2432,7 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>120</v>
+        <v>206</v>
       </c>
       <c r="B71" t="s">
         <v>47</v>
@@ -2024,7 +2440,7 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>121</v>
+        <v>207</v>
       </c>
       <c r="B72" t="s">
         <v>49</v>
@@ -2032,7 +2448,7 @@
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>122</v>
+        <v>208</v>
       </c>
       <c r="B73" t="s">
         <v>51</v>
@@ -2040,7 +2456,7 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>123</v>
+        <v>209</v>
       </c>
       <c r="B74" t="s">
         <v>53</v>
@@ -2048,7 +2464,7 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>124</v>
+        <v>210</v>
       </c>
       <c r="B75" t="s">
         <v>55</v>
@@ -2056,7 +2472,7 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>125</v>
+        <v>211</v>
       </c>
       <c r="B76" t="s">
         <v>57</v>
@@ -2064,7 +2480,7 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>126</v>
+        <v>212</v>
       </c>
       <c r="B77" t="s">
         <v>59</v>
@@ -2072,7 +2488,7 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>127</v>
+        <v>213</v>
       </c>
       <c r="B78" t="s">
         <v>57</v>
@@ -2080,7 +2496,7 @@
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>128</v>
+        <v>214</v>
       </c>
       <c r="B79" t="s">
         <v>59</v>
@@ -2088,7 +2504,7 @@
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>129</v>
+        <v>215</v>
       </c>
       <c r="B80" t="s">
         <v>57</v>
@@ -2096,7 +2512,7 @@
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>130</v>
+        <v>216</v>
       </c>
       <c r="B81" t="s">
         <v>59</v>
@@ -2104,7 +2520,7 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>131</v>
+        <v>217</v>
       </c>
       <c r="B82" t="s">
         <v>57</v>
@@ -2112,7 +2528,7 @@
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>132</v>
+        <v>218</v>
       </c>
       <c r="B83" t="s">
         <v>59</v>
@@ -2120,7 +2536,7 @@
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>133</v>
+        <v>219</v>
       </c>
       <c r="B84" t="s">
         <v>57</v>
@@ -2128,7 +2544,7 @@
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>134</v>
+        <v>220</v>
       </c>
       <c r="B85" s="9" t="s">
         <v>59</v>
@@ -2136,7 +2552,7 @@
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>135</v>
+        <v>221</v>
       </c>
       <c r="B86" s="9" t="s">
         <v>57</v>
@@ -2144,23 +2560,23 @@
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>136</v>
+        <v>222</v>
       </c>
       <c r="B87" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>137</v>
+        <v>223</v>
       </c>
       <c r="B88" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>138</v>
+        <v>224</v>
       </c>
       <c r="B89" t="s">
         <v>10</v>
@@ -2168,7 +2584,7 @@
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>139</v>
+        <v>225</v>
       </c>
       <c r="B90" t="s">
         <v>12</v>
@@ -2176,7 +2592,7 @@
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>140</v>
+        <v>226</v>
       </c>
       <c r="B91" t="s">
         <v>13</v>
@@ -2184,7 +2600,7 @@
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>141</v>
+        <v>227</v>
       </c>
       <c r="B92" t="s">
         <v>15</v>
@@ -2192,7 +2608,7 @@
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>142</v>
+        <v>228</v>
       </c>
       <c r="B93" t="s">
         <v>16</v>
@@ -2200,7 +2616,7 @@
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>143</v>
+        <v>229</v>
       </c>
       <c r="B94" t="s">
         <v>18</v>
@@ -2208,23 +2624,23 @@
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>144</v>
+        <v>230</v>
       </c>
       <c r="B95" t="s">
-        <v>178</v>
+        <v>136</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>145</v>
+        <v>231</v>
       </c>
       <c r="B96" t="s">
-        <v>179</v>
+        <v>137</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>146</v>
+        <v>232</v>
       </c>
       <c r="B97" t="s">
         <v>19</v>
@@ -2232,7 +2648,7 @@
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>147</v>
+        <v>233</v>
       </c>
       <c r="B98" t="s">
         <v>21</v>
@@ -2240,23 +2656,23 @@
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>176</v>
+        <v>234</v>
       </c>
       <c r="B99" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>177</v>
+        <v>235</v>
       </c>
       <c r="B100" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>148</v>
+        <v>236</v>
       </c>
       <c r="B101" t="s">
         <v>23</v>
@@ -2264,7 +2680,7 @@
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>149</v>
+        <v>237</v>
       </c>
       <c r="B102" t="s">
         <v>25</v>
@@ -2272,7 +2688,7 @@
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>150</v>
+        <v>238</v>
       </c>
       <c r="B103" t="s">
         <v>27</v>
@@ -2280,7 +2696,7 @@
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>151</v>
+        <v>239</v>
       </c>
       <c r="B104" t="s">
         <v>29</v>
@@ -2288,7 +2704,7 @@
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>152</v>
+        <v>240</v>
       </c>
       <c r="B105" t="s">
         <v>31</v>
@@ -2296,7 +2712,7 @@
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>153</v>
+        <v>241</v>
       </c>
       <c r="B106" t="s">
         <v>33</v>
@@ -2304,7 +2720,7 @@
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>154</v>
+        <v>242</v>
       </c>
       <c r="B107" t="s">
         <v>35</v>
@@ -2312,7 +2728,7 @@
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>155</v>
+        <v>243</v>
       </c>
       <c r="B108" t="s">
         <v>37</v>
@@ -2320,7 +2736,7 @@
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>156</v>
+        <v>244</v>
       </c>
       <c r="B109" t="s">
         <v>39</v>
@@ -2328,7 +2744,7 @@
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>157</v>
+        <v>245</v>
       </c>
       <c r="B110" t="s">
         <v>41</v>
@@ -2336,7 +2752,7 @@
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>158</v>
+        <v>246</v>
       </c>
       <c r="B111" t="s">
         <v>43</v>
@@ -2344,7 +2760,7 @@
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>159</v>
+        <v>247</v>
       </c>
       <c r="B112" t="s">
         <v>45</v>
@@ -2352,7 +2768,7 @@
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>160</v>
+        <v>248</v>
       </c>
       <c r="B113" t="s">
         <v>47</v>
@@ -2360,7 +2776,7 @@
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>161</v>
+        <v>249</v>
       </c>
       <c r="B114" t="s">
         <v>49</v>
@@ -2368,7 +2784,7 @@
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>162</v>
+        <v>250</v>
       </c>
       <c r="B115" t="s">
         <v>51</v>
@@ -2376,7 +2792,7 @@
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>163</v>
+        <v>251</v>
       </c>
       <c r="B116" t="s">
         <v>53</v>
@@ -2384,7 +2800,7 @@
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>164</v>
+        <v>252</v>
       </c>
       <c r="B117" t="s">
         <v>55</v>
@@ -2392,7 +2808,7 @@
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>165</v>
+        <v>253</v>
       </c>
       <c r="B118" t="s">
         <v>57</v>
@@ -2400,7 +2816,7 @@
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>166</v>
+        <v>254</v>
       </c>
       <c r="B119" t="s">
         <v>59</v>
@@ -2408,7 +2824,7 @@
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>167</v>
+        <v>255</v>
       </c>
       <c r="B120" t="s">
         <v>57</v>
@@ -2416,7 +2832,7 @@
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>168</v>
+        <v>256</v>
       </c>
       <c r="B121" t="s">
         <v>59</v>
@@ -2424,7 +2840,7 @@
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>169</v>
+        <v>257</v>
       </c>
       <c r="B122" t="s">
         <v>57</v>
@@ -2432,7 +2848,7 @@
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>170</v>
+        <v>258</v>
       </c>
       <c r="B123" t="s">
         <v>59</v>
@@ -2440,7 +2856,7 @@
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>171</v>
+        <v>259</v>
       </c>
       <c r="B124" t="s">
         <v>57</v>
@@ -2448,7 +2864,7 @@
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>172</v>
+        <v>260</v>
       </c>
       <c r="B125" t="s">
         <v>59</v>
@@ -2456,7 +2872,7 @@
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>173</v>
+        <v>261</v>
       </c>
       <c r="B126" t="s">
         <v>57</v>
@@ -2464,7 +2880,7 @@
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>174</v>
+        <v>262</v>
       </c>
       <c r="B127" s="9" t="s">
         <v>59</v>
@@ -2472,9 +2888,1017 @@
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
+        <v>263</v>
+      </c>
+      <c r="B128" s="9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A129" t="s">
+        <v>138</v>
+      </c>
+      <c r="B129" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A130" t="s">
+        <v>139</v>
+      </c>
+      <c r="B130" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A131" t="s">
+        <v>140</v>
+      </c>
+      <c r="B131" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A132" t="s">
+        <v>141</v>
+      </c>
+      <c r="B132" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A133" t="s">
+        <v>142</v>
+      </c>
+      <c r="B133" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A134" t="s">
+        <v>143</v>
+      </c>
+      <c r="B134" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A135" t="s">
+        <v>144</v>
+      </c>
+      <c r="B135" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A136" t="s">
+        <v>145</v>
+      </c>
+      <c r="B136" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A137" t="s">
+        <v>146</v>
+      </c>
+      <c r="B137" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A138" t="s">
+        <v>147</v>
+      </c>
+      <c r="B138" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A139" t="s">
+        <v>148</v>
+      </c>
+      <c r="B139" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A140" t="s">
+        <v>149</v>
+      </c>
+      <c r="B140" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A141" t="s">
+        <v>150</v>
+      </c>
+      <c r="B141" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A142" t="s">
+        <v>151</v>
+      </c>
+      <c r="B142" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A143" t="s">
+        <v>152</v>
+      </c>
+      <c r="B143" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A144" t="s">
+        <v>153</v>
+      </c>
+      <c r="B144" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A145" t="s">
+        <v>154</v>
+      </c>
+      <c r="B145" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A146" t="s">
+        <v>155</v>
+      </c>
+      <c r="B146" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A147" t="s">
+        <v>156</v>
+      </c>
+      <c r="B147" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A148" t="s">
+        <v>157</v>
+      </c>
+      <c r="B148" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A149" t="s">
+        <v>158</v>
+      </c>
+      <c r="B149" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A150" t="s">
+        <v>159</v>
+      </c>
+      <c r="B150" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A151" t="s">
+        <v>160</v>
+      </c>
+      <c r="B151" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A152" t="s">
+        <v>161</v>
+      </c>
+      <c r="B152" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A153" t="s">
+        <v>162</v>
+      </c>
+      <c r="B153" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A154" t="s">
+        <v>163</v>
+      </c>
+      <c r="B154" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A155" t="s">
+        <v>164</v>
+      </c>
+      <c r="B155" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A156" t="s">
+        <v>165</v>
+      </c>
+      <c r="B156" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A157" t="s">
+        <v>166</v>
+      </c>
+      <c r="B157" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A158" t="s">
+        <v>167</v>
+      </c>
+      <c r="B158" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A159" t="s">
+        <v>168</v>
+      </c>
+      <c r="B159" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A160" t="s">
+        <v>169</v>
+      </c>
+      <c r="B160" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A161" t="s">
+        <v>170</v>
+      </c>
+      <c r="B161" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A162" t="s">
+        <v>171</v>
+      </c>
+      <c r="B162" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A163" t="s">
+        <v>172</v>
+      </c>
+      <c r="B163" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A164" t="s">
+        <v>173</v>
+      </c>
+      <c r="B164" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A165" t="s">
+        <v>174</v>
+      </c>
+      <c r="B165" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A166" t="s">
         <v>175</v>
       </c>
-      <c r="B128" s="9" t="s">
+      <c r="B166" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A167" t="s">
+        <v>176</v>
+      </c>
+      <c r="B167" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A168" t="s">
+        <v>177</v>
+      </c>
+      <c r="B168" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A169" t="s">
+        <v>178</v>
+      </c>
+      <c r="B169" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A170" t="s">
+        <v>179</v>
+      </c>
+      <c r="B170" s="9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A171" t="s">
+        <v>264</v>
+      </c>
+      <c r="B171" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A172" t="s">
+        <v>265</v>
+      </c>
+      <c r="B172" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A173" t="s">
+        <v>266</v>
+      </c>
+      <c r="B173" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A174" t="s">
+        <v>267</v>
+      </c>
+      <c r="B174" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A175" t="s">
+        <v>268</v>
+      </c>
+      <c r="B175" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A176" t="s">
+        <v>269</v>
+      </c>
+      <c r="B176" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A177" t="s">
+        <v>270</v>
+      </c>
+      <c r="B177" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A178" t="s">
+        <v>271</v>
+      </c>
+      <c r="B178" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A179" t="s">
+        <v>272</v>
+      </c>
+      <c r="B179" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A180" t="s">
+        <v>273</v>
+      </c>
+      <c r="B180" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A181" t="s">
+        <v>274</v>
+      </c>
+      <c r="B181" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A182" t="s">
+        <v>275</v>
+      </c>
+      <c r="B182" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A183" t="s">
+        <v>276</v>
+      </c>
+      <c r="B183" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A184" t="s">
+        <v>277</v>
+      </c>
+      <c r="B184" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A185" t="s">
+        <v>278</v>
+      </c>
+      <c r="B185" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A186" t="s">
+        <v>279</v>
+      </c>
+      <c r="B186" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A187" t="s">
+        <v>280</v>
+      </c>
+      <c r="B187" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A188" t="s">
+        <v>281</v>
+      </c>
+      <c r="B188" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A189" t="s">
+        <v>282</v>
+      </c>
+      <c r="B189" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A190" t="s">
+        <v>283</v>
+      </c>
+      <c r="B190" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A191" t="s">
+        <v>284</v>
+      </c>
+      <c r="B191" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A192" t="s">
+        <v>285</v>
+      </c>
+      <c r="B192" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A193" t="s">
+        <v>286</v>
+      </c>
+      <c r="B193" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A194" t="s">
+        <v>287</v>
+      </c>
+      <c r="B194" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A195" t="s">
+        <v>288</v>
+      </c>
+      <c r="B195" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A196" t="s">
+        <v>289</v>
+      </c>
+      <c r="B196" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A197" t="s">
+        <v>290</v>
+      </c>
+      <c r="B197" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A198" t="s">
+        <v>291</v>
+      </c>
+      <c r="B198" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A199" t="s">
+        <v>292</v>
+      </c>
+      <c r="B199" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A200" t="s">
+        <v>293</v>
+      </c>
+      <c r="B200" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A201" t="s">
+        <v>294</v>
+      </c>
+      <c r="B201" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A202" t="s">
+        <v>295</v>
+      </c>
+      <c r="B202" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A203" t="s">
+        <v>296</v>
+      </c>
+      <c r="B203" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A204" t="s">
+        <v>297</v>
+      </c>
+      <c r="B204" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A205" t="s">
+        <v>298</v>
+      </c>
+      <c r="B205" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A206" t="s">
+        <v>299</v>
+      </c>
+      <c r="B206" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A207" t="s">
+        <v>300</v>
+      </c>
+      <c r="B207" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A208" t="s">
+        <v>301</v>
+      </c>
+      <c r="B208" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A209" t="s">
+        <v>302</v>
+      </c>
+      <c r="B209" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A210" t="s">
+        <v>303</v>
+      </c>
+      <c r="B210" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A211" t="s">
+        <v>304</v>
+      </c>
+      <c r="B211" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A212" t="s">
+        <v>305</v>
+      </c>
+      <c r="B212" s="9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A213" t="s">
+        <v>94</v>
+      </c>
+      <c r="B213" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A214" t="s">
+        <v>95</v>
+      </c>
+      <c r="B214" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A215" t="s">
+        <v>96</v>
+      </c>
+      <c r="B215" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A216" t="s">
+        <v>97</v>
+      </c>
+      <c r="B216" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A217" t="s">
+        <v>98</v>
+      </c>
+      <c r="B217" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A218" t="s">
+        <v>99</v>
+      </c>
+      <c r="B218" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A219" t="s">
+        <v>100</v>
+      </c>
+      <c r="B219" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A220" t="s">
+        <v>101</v>
+      </c>
+      <c r="B220" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A221" t="s">
+        <v>102</v>
+      </c>
+      <c r="B221" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A222" t="s">
+        <v>103</v>
+      </c>
+      <c r="B222" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A223" t="s">
+        <v>104</v>
+      </c>
+      <c r="B223" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A224" t="s">
+        <v>105</v>
+      </c>
+      <c r="B224" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A225" t="s">
+        <v>134</v>
+      </c>
+      <c r="B225" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A226" t="s">
+        <v>135</v>
+      </c>
+      <c r="B226" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A227" t="s">
+        <v>106</v>
+      </c>
+      <c r="B227" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A228" t="s">
+        <v>107</v>
+      </c>
+      <c r="B228" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A229" t="s">
+        <v>108</v>
+      </c>
+      <c r="B229" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A230" t="s">
+        <v>109</v>
+      </c>
+      <c r="B230" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A231" t="s">
+        <v>110</v>
+      </c>
+      <c r="B231" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A232" t="s">
+        <v>111</v>
+      </c>
+      <c r="B232" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A233" t="s">
+        <v>112</v>
+      </c>
+      <c r="B233" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A234" t="s">
+        <v>113</v>
+      </c>
+      <c r="B234" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A235" t="s">
+        <v>114</v>
+      </c>
+      <c r="B235" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A236" t="s">
+        <v>115</v>
+      </c>
+      <c r="B236" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A237" t="s">
+        <v>116</v>
+      </c>
+      <c r="B237" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A238" t="s">
+        <v>117</v>
+      </c>
+      <c r="B238" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A239" t="s">
+        <v>118</v>
+      </c>
+      <c r="B239" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A240" t="s">
+        <v>119</v>
+      </c>
+      <c r="B240" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A241" t="s">
+        <v>120</v>
+      </c>
+      <c r="B241" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A242" t="s">
+        <v>121</v>
+      </c>
+      <c r="B242" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A243" t="s">
+        <v>122</v>
+      </c>
+      <c r="B243" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A244" t="s">
+        <v>123</v>
+      </c>
+      <c r="B244" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A245" t="s">
+        <v>124</v>
+      </c>
+      <c r="B245" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A246" t="s">
+        <v>125</v>
+      </c>
+      <c r="B246" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A247" t="s">
+        <v>126</v>
+      </c>
+      <c r="B247" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A248" t="s">
+        <v>127</v>
+      </c>
+      <c r="B248" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A249" t="s">
+        <v>128</v>
+      </c>
+      <c r="B249" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A250" t="s">
+        <v>129</v>
+      </c>
+      <c r="B250" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A251" t="s">
+        <v>130</v>
+      </c>
+      <c r="B251" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A252" t="s">
+        <v>131</v>
+      </c>
+      <c r="B252" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A253" t="s">
+        <v>132</v>
+      </c>
+      <c r="B253" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A254" t="s">
+        <v>133</v>
+      </c>
+      <c r="B254" s="9" t="s">
         <v>57</v>
       </c>
     </row>
